--- a/output/pdf_financials_xlsx/WINS.xlsx
+++ b/output/pdf_financials_xlsx/WINS.xlsx
@@ -4288,19 +4288,19 @@
         <v>11.806636</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.883288</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>12.046136</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.182327</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>11.74311</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>11.906571</v>
       </c>
     </row>
     <row r="93">
@@ -6687,7 +6687,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -9516,7 +9520,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WINS.xlsx
+++ b/output/pdf_financials_xlsx/WINS.xlsx
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.01292</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008888</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.004848</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.000151</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.005181</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>-0.000668</v>
@@ -892,7 +892,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.142646</v>
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
@@ -1559,19 +1559,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.660749</v>
+        <v>-3.673669</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.891985</v>
+        <v>-1.900873</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.182035</v>
+        <v>-0.186883</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-2.271093</v>
+        <v>-2.271244</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.07222099999999999</v>
+        <v>-0.077402</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-1.371932</v>
@@ -1586,7 +1586,7 @@
         <v>-0.973757</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.973757</v>
+        <v>-1.116403</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -1643,19 +1643,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.660749</v>
+        <v>-3.673669</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.891985</v>
+        <v>-1.900873</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.182035</v>
+        <v>-0.186883</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-2.271093</v>
+        <v>-2.271244</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.07222099999999999</v>
+        <v>-0.077402</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-1.371932</v>
@@ -1670,7 +1670,7 @@
         <v>-0.973757</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.973757</v>
+        <v>-1.116403</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -1858,37 +1858,37 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.260964</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.728023</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.312324</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.328118</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.016221</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.232933</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.690148</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.31545</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.137046</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>3.149066</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.363845</v>
       </c>
     </row>
     <row r="35">
@@ -1938,37 +1938,37 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.0275</v>
+        <v>1.288464</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.753023</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.910892</v>
+        <v>1.223216</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.353118</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.041221</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.242933</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.690148</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.31545</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.137046</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>3.149066</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.363845</v>
       </c>
     </row>
     <row r="37">
@@ -2418,22 +2418,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.604646</v>
+        <v>0.343682</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.824586</v>
+        <v>0.096563</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.415713</v>
+        <v>0.103389</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.353878</v>
+        <v>0.02576</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.126425</v>
+        <v>0.110204</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.294035</v>
+        <v>0.061102</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0</v>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -20912,7 +20912,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E303" s="5" t="n">

--- a/output/pdf_financials_xlsx/WINS.xlsx
+++ b/output/pdf_financials_xlsx/WINS.xlsx
@@ -4610,10 +4610,10 @@
         <v>0</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.067772</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.06775200000000001</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>0</v>
@@ -4810,10 +4810,10 @@
         <v>-0.286923</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.09042699999999999</v>
+        <v>0.158199</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.122403</v>
+        <v>0.054651</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.017514</v>
@@ -5167,10 +5167,10 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.422488</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.885892</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.02406</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -15091,7 +15091,11 @@
           <t>Proceeds from disposal of investments 7</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -16126,7 +16130,11 @@
           <t>Recovery of GST receivable</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -17601,7 +17609,11 @@
           <t>(Recovery) Provision for GST receivable</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -17952,7 +17964,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -18567,7 +18583,11 @@
           <t>Provision for GST receivable</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
